--- a/AAISM Quiz Questions.xlsx
+++ b/AAISM Quiz Questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhavnaw\Downloads\ISACA Advanced in AI Security Management (AAISM)\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A03B4893-9581-428A-B7B4-9D0D95D70EE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{888DE509-A0AA-4F5E-82C3-049981CFCD96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <definedName name="In_Process">#REF!</definedName>
     <definedName name="STATUS">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -3547,11 +3547,6 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="2"/>
     </xf>
@@ -3560,6 +3555,11 @@
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Chapter" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -3893,13 +3893,13 @@
       <c r="N1" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="40" t="s">
+      <c r="O1" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="41"/>
-      <c r="R1" s="41"/>
-      <c r="S1" s="42"/>
+      <c r="P1" s="45"/>
+      <c r="Q1" s="45"/>
+      <c r="R1" s="45"/>
+      <c r="S1" s="46"/>
     </row>
     <row r="2" spans="1:19" s="12" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
@@ -5770,30 +5770,30 @@
       </c>
     </row>
     <row r="2" spans="1:9" s="31" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="46"/>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
     </row>
     <row r="3" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="43" t="s">
+      <c r="A3" s="40" t="s">
         <v>210</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="44"/>
-      <c r="I3" s="44"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
     </row>
     <row r="4" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
@@ -5854,17 +5854,17 @@
       </c>
     </row>
     <row r="6" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="43" t="s">
+      <c r="A6" s="40" t="s">
         <v>225</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
@@ -5925,17 +5925,17 @@
       </c>
     </row>
     <row r="9" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="40" t="s">
         <v>240</v>
       </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
     </row>
     <row r="10" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="35" t="s">
@@ -6025,17 +6025,17 @@
       </c>
     </row>
     <row r="13" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="40" t="s">
         <v>261</v>
       </c>
-      <c r="B13" s="44"/>
-      <c r="C13" s="44"/>
-      <c r="D13" s="44"/>
-      <c r="E13" s="44"/>
-      <c r="F13" s="44"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="44"/>
-      <c r="I13" s="44"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
     </row>
     <row r="14" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="35" t="s">
@@ -6096,17 +6096,17 @@
       </c>
     </row>
     <row r="16" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="40" t="s">
         <v>276</v>
       </c>
-      <c r="B16" s="44"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="44"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="44"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
     </row>
     <row r="17" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="35" t="s">
@@ -6167,17 +6167,17 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="43" t="s">
+      <c r="A19" s="40" t="s">
         <v>290</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="41"/>
+      <c r="I19" s="41"/>
     </row>
     <row r="20" spans="1:9" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="35" t="s">
@@ -6238,17 +6238,17 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="40" t="s">
         <v>305</v>
       </c>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
-      <c r="D22" s="44"/>
-      <c r="E22" s="44"/>
-      <c r="F22" s="44"/>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="I22" s="44"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
     </row>
     <row r="23" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="35" t="s">
@@ -6309,30 +6309,30 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="31" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="45" t="s">
+      <c r="A25" s="42" t="s">
         <v>320</v>
       </c>
-      <c r="B25" s="46"/>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="46"/>
-      <c r="G25" s="46"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="43"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="43"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
     </row>
     <row r="26" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="43" t="s">
+      <c r="A26" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="41"/>
+      <c r="H26" s="41"/>
+      <c r="I26" s="41"/>
     </row>
     <row r="27" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="35" t="s">
@@ -6393,17 +6393,17 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="43" t="s">
+      <c r="A29" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
     </row>
     <row r="30" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="35" t="s">
@@ -6435,17 +6435,17 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="43" t="s">
+      <c r="A31" s="40" t="s">
         <v>345</v>
       </c>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="44"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="41"/>
+      <c r="H31" s="41"/>
+      <c r="I31" s="41"/>
     </row>
     <row r="32" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="35" t="s">
@@ -6477,17 +6477,17 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="43" t="s">
+      <c r="A33" s="40" t="s">
         <v>354</v>
       </c>
-      <c r="B33" s="44"/>
-      <c r="C33" s="44"/>
-      <c r="D33" s="44"/>
-      <c r="E33" s="44"/>
-      <c r="F33" s="44"/>
-      <c r="G33" s="44"/>
-      <c r="H33" s="44"/>
-      <c r="I33" s="44"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="41"/>
+      <c r="H33" s="41"/>
+      <c r="I33" s="41"/>
     </row>
     <row r="34" spans="1:9" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="35" t="s">
@@ -6577,17 +6577,17 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="43" t="s">
+      <c r="A37" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="B37" s="44"/>
-      <c r="C37" s="44"/>
-      <c r="D37" s="44"/>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-      <c r="I37" s="44"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="41"/>
+      <c r="H37" s="41"/>
+      <c r="I37" s="41"/>
     </row>
     <row r="38" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="35" t="s">
@@ -6619,17 +6619,17 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="43" t="s">
+      <c r="A39" s="40" t="s">
         <v>384</v>
       </c>
-      <c r="B39" s="44"/>
-      <c r="C39" s="44"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-      <c r="I39" s="44"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="41"/>
     </row>
     <row r="40" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="35" t="s">
@@ -6661,17 +6661,17 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="43" t="s">
+      <c r="A41" s="40" t="s">
         <v>393</v>
       </c>
-      <c r="B41" s="44"/>
-      <c r="C41" s="44"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-      <c r="I41" s="44"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
     </row>
     <row r="42" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="35" t="s">
@@ -6703,17 +6703,17 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="43" t="s">
+      <c r="A43" s="40" t="s">
         <v>402</v>
       </c>
-      <c r="B43" s="44"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-      <c r="I43" s="44"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="41"/>
+      <c r="H43" s="41"/>
+      <c r="I43" s="41"/>
     </row>
     <row r="44" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="35" t="s">
@@ -6745,30 +6745,30 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="31" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="45" t="s">
+      <c r="A45" s="42" t="s">
         <v>411</v>
       </c>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="46"/>
-      <c r="F45" s="46"/>
-      <c r="G45" s="46"/>
-      <c r="H45" s="46"/>
-      <c r="I45" s="46"/>
+      <c r="B45" s="43"/>
+      <c r="C45" s="43"/>
+      <c r="D45" s="43"/>
+      <c r="E45" s="43"/>
+      <c r="F45" s="43"/>
+      <c r="G45" s="43"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
     </row>
     <row r="46" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="43" t="s">
+      <c r="A46" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-      <c r="I46" s="44"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="41"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="41"/>
+      <c r="H46" s="41"/>
+      <c r="I46" s="41"/>
     </row>
     <row r="47" spans="1:9" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="35" t="s">
@@ -6800,17 +6800,17 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="43" t="s">
+      <c r="A48" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="44"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="41"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="41"/>
+      <c r="H48" s="41"/>
+      <c r="I48" s="41"/>
     </row>
     <row r="49" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="35" t="s">
@@ -6900,17 +6900,17 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="43" t="s">
+      <c r="A52" s="40" t="s">
         <v>442</v>
       </c>
-      <c r="B52" s="44"/>
-      <c r="C52" s="44"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="44"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="44"/>
-      <c r="I52" s="44"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="41"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="41"/>
+      <c r="H52" s="41"/>
+      <c r="I52" s="41"/>
     </row>
     <row r="53" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="35" t="s">
@@ -6942,17 +6942,17 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="43" t="s">
+      <c r="A54" s="40" t="s">
         <v>451</v>
       </c>
-      <c r="B54" s="44"/>
-      <c r="C54" s="44"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
-      <c r="G54" s="44"/>
-      <c r="H54" s="44"/>
-      <c r="I54" s="44"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="41"/>
+      <c r="E54" s="41"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="41"/>
+      <c r="H54" s="41"/>
+      <c r="I54" s="41"/>
     </row>
     <row r="55" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="35" t="s">
@@ -6984,17 +6984,17 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="43" t="s">
+      <c r="A56" s="40" t="s">
         <v>460</v>
       </c>
-      <c r="B56" s="44"/>
-      <c r="C56" s="44"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="44"/>
-      <c r="I56" s="44"/>
+      <c r="B56" s="41"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="41"/>
+      <c r="E56" s="41"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="41"/>
+      <c r="H56" s="41"/>
+      <c r="I56" s="41"/>
     </row>
     <row r="57" spans="1:9" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
@@ -7026,17 +7026,17 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="43" t="s">
+      <c r="A58" s="40" t="s">
         <v>469</v>
       </c>
-      <c r="B58" s="44"/>
-      <c r="C58" s="44"/>
-      <c r="D58" s="44"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="44"/>
-      <c r="H58" s="44"/>
-      <c r="I58" s="44"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="41"/>
+      <c r="E58" s="41"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="41"/>
+      <c r="H58" s="41"/>
+      <c r="I58" s="41"/>
     </row>
     <row r="59" spans="1:9" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="35" t="s">
@@ -7126,17 +7126,17 @@
       </c>
     </row>
     <row r="62" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="43" t="s">
+      <c r="A62" s="40" t="s">
         <v>490</v>
       </c>
-      <c r="B62" s="44"/>
-      <c r="C62" s="44"/>
-      <c r="D62" s="44"/>
-      <c r="E62" s="44"/>
-      <c r="F62" s="44"/>
-      <c r="G62" s="44"/>
-      <c r="H62" s="44"/>
-      <c r="I62" s="44"/>
+      <c r="B62" s="41"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="41"/>
+      <c r="E62" s="41"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="41"/>
+      <c r="H62" s="41"/>
+      <c r="I62" s="41"/>
     </row>
     <row r="63" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="35" t="s">
@@ -7197,17 +7197,17 @@
       </c>
     </row>
     <row r="65" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="43" t="s">
+      <c r="A65" s="40" t="s">
         <v>505</v>
       </c>
-      <c r="B65" s="44"/>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
+      <c r="B65" s="41"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="41"/>
+      <c r="E65" s="41"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="41"/>
+      <c r="H65" s="41"/>
+      <c r="I65" s="41"/>
     </row>
     <row r="66" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="35" t="s">
@@ -7268,30 +7268,30 @@
       </c>
     </row>
     <row r="68" spans="1:9" s="31" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="45" t="s">
+      <c r="A68" s="42" t="s">
         <v>520</v>
       </c>
-      <c r="B68" s="46"/>
-      <c r="C68" s="46"/>
-      <c r="D68" s="46"/>
-      <c r="E68" s="46"/>
-      <c r="F68" s="46"/>
-      <c r="G68" s="46"/>
-      <c r="H68" s="46"/>
-      <c r="I68" s="46"/>
+      <c r="B68" s="43"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+      <c r="H68" s="43"/>
+      <c r="I68" s="43"/>
     </row>
     <row r="69" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="43" t="s">
+      <c r="A69" s="40" t="s">
         <v>521</v>
       </c>
-      <c r="B69" s="44"/>
-      <c r="C69" s="44"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="44"/>
-      <c r="G69" s="44"/>
-      <c r="H69" s="44"/>
-      <c r="I69" s="44"/>
+      <c r="B69" s="41"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="41"/>
+      <c r="E69" s="41"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="41"/>
+      <c r="H69" s="41"/>
+      <c r="I69" s="41"/>
     </row>
     <row r="70" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="35" t="s">
@@ -7352,17 +7352,17 @@
       </c>
     </row>
     <row r="72" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="43" t="s">
+      <c r="A72" s="40" t="s">
         <v>536</v>
       </c>
-      <c r="B72" s="44"/>
-      <c r="C72" s="44"/>
-      <c r="D72" s="44"/>
-      <c r="E72" s="44"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="44"/>
-      <c r="H72" s="44"/>
-      <c r="I72" s="44"/>
+      <c r="B72" s="41"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="41"/>
+      <c r="E72" s="41"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="41"/>
+      <c r="H72" s="41"/>
+      <c r="I72" s="41"/>
     </row>
     <row r="73" spans="1:9" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="35" t="s">
@@ -7423,17 +7423,17 @@
       </c>
     </row>
     <row r="75" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="43" t="s">
+      <c r="A75" s="40" t="s">
         <v>551</v>
       </c>
-      <c r="B75" s="44"/>
-      <c r="C75" s="44"/>
-      <c r="D75" s="44"/>
-      <c r="E75" s="44"/>
-      <c r="F75" s="44"/>
-      <c r="G75" s="44"/>
-      <c r="H75" s="44"/>
-      <c r="I75" s="44"/>
+      <c r="B75" s="41"/>
+      <c r="C75" s="41"/>
+      <c r="D75" s="41"/>
+      <c r="E75" s="41"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="41"/>
     </row>
     <row r="76" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="35" t="s">
@@ -7523,17 +7523,17 @@
       </c>
     </row>
     <row r="79" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="43" t="s">
+      <c r="A79" s="40" t="s">
         <v>572</v>
       </c>
-      <c r="B79" s="44"/>
-      <c r="C79" s="44"/>
-      <c r="D79" s="44"/>
-      <c r="E79" s="44"/>
-      <c r="F79" s="44"/>
-      <c r="G79" s="44"/>
-      <c r="H79" s="44"/>
-      <c r="I79" s="44"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="41"/>
+      <c r="E79" s="41"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="41"/>
+      <c r="H79" s="41"/>
+      <c r="I79" s="41"/>
     </row>
     <row r="80" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="35" t="s">
@@ -7623,17 +7623,17 @@
       </c>
     </row>
     <row r="83" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="43" t="s">
+      <c r="A83" s="40" t="s">
         <v>593</v>
       </c>
-      <c r="B83" s="44"/>
-      <c r="C83" s="44"/>
-      <c r="D83" s="44"/>
-      <c r="E83" s="44"/>
-      <c r="F83" s="44"/>
-      <c r="G83" s="44"/>
-      <c r="H83" s="44"/>
-      <c r="I83" s="44"/>
+      <c r="B83" s="41"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="41"/>
+      <c r="E83" s="41"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="41"/>
+      <c r="H83" s="41"/>
+      <c r="I83" s="41"/>
     </row>
     <row r="84" spans="1:9" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="35" t="s">
@@ -7723,17 +7723,17 @@
       </c>
     </row>
     <row r="87" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="43" t="s">
+      <c r="A87" s="40" t="s">
         <v>614</v>
       </c>
-      <c r="B87" s="44"/>
-      <c r="C87" s="44"/>
-      <c r="D87" s="44"/>
-      <c r="E87" s="44"/>
-      <c r="F87" s="44"/>
-      <c r="G87" s="44"/>
-      <c r="H87" s="44"/>
-      <c r="I87" s="44"/>
+      <c r="B87" s="41"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="41"/>
+      <c r="E87" s="41"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="41"/>
+      <c r="H87" s="41"/>
+      <c r="I87" s="41"/>
     </row>
     <row r="88" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="35" t="s">
@@ -7794,17 +7794,17 @@
       </c>
     </row>
     <row r="90" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="43" t="s">
+      <c r="A90" s="40" t="s">
         <v>629</v>
       </c>
-      <c r="B90" s="44"/>
-      <c r="C90" s="44"/>
-      <c r="D90" s="44"/>
-      <c r="E90" s="44"/>
-      <c r="F90" s="44"/>
-      <c r="G90" s="44"/>
-      <c r="H90" s="44"/>
-      <c r="I90" s="44"/>
+      <c r="B90" s="41"/>
+      <c r="C90" s="41"/>
+      <c r="D90" s="41"/>
+      <c r="E90" s="41"/>
+      <c r="F90" s="41"/>
+      <c r="G90" s="41"/>
+      <c r="H90" s="41"/>
+      <c r="I90" s="41"/>
     </row>
     <row r="91" spans="1:9" s="31" customFormat="1" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="35" t="s">
@@ -7894,17 +7894,17 @@
       </c>
     </row>
     <row r="94" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="43" t="s">
+      <c r="A94" s="40" t="s">
         <v>650</v>
       </c>
-      <c r="B94" s="44"/>
-      <c r="C94" s="44"/>
-      <c r="D94" s="44"/>
-      <c r="E94" s="44"/>
-      <c r="F94" s="44"/>
-      <c r="G94" s="44"/>
-      <c r="H94" s="44"/>
-      <c r="I94" s="44"/>
+      <c r="B94" s="41"/>
+      <c r="C94" s="41"/>
+      <c r="D94" s="41"/>
+      <c r="E94" s="41"/>
+      <c r="F94" s="41"/>
+      <c r="G94" s="41"/>
+      <c r="H94" s="41"/>
+      <c r="I94" s="41"/>
     </row>
     <row r="95" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="35" t="s">
@@ -7994,30 +7994,30 @@
       </c>
     </row>
     <row r="98" spans="1:9" s="31" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="45" t="s">
+      <c r="A98" s="42" t="s">
         <v>671</v>
       </c>
-      <c r="B98" s="46"/>
-      <c r="C98" s="46"/>
-      <c r="D98" s="46"/>
-      <c r="E98" s="46"/>
-      <c r="F98" s="46"/>
-      <c r="G98" s="46"/>
-      <c r="H98" s="46"/>
-      <c r="I98" s="46"/>
+      <c r="B98" s="43"/>
+      <c r="C98" s="43"/>
+      <c r="D98" s="43"/>
+      <c r="E98" s="43"/>
+      <c r="F98" s="43"/>
+      <c r="G98" s="43"/>
+      <c r="H98" s="43"/>
+      <c r="I98" s="43"/>
     </row>
     <row r="99" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="43" t="s">
+      <c r="A99" s="40" t="s">
         <v>672</v>
       </c>
-      <c r="B99" s="44"/>
-      <c r="C99" s="44"/>
-      <c r="D99" s="44"/>
-      <c r="E99" s="44"/>
-      <c r="F99" s="44"/>
-      <c r="G99" s="44"/>
-      <c r="H99" s="44"/>
-      <c r="I99" s="44"/>
+      <c r="B99" s="41"/>
+      <c r="C99" s="41"/>
+      <c r="D99" s="41"/>
+      <c r="E99" s="41"/>
+      <c r="F99" s="41"/>
+      <c r="G99" s="41"/>
+      <c r="H99" s="41"/>
+      <c r="I99" s="41"/>
     </row>
     <row r="100" spans="1:9" s="31" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="35" t="s">
@@ -8107,17 +8107,17 @@
       </c>
     </row>
     <row r="103" spans="1:9" s="31" customFormat="1" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="43" t="s">
+      <c r="A103" s="40" t="s">
         <v>693</v>
       </c>
-      <c r="B103" s="44"/>
-      <c r="C103" s="44"/>
-      <c r="D103" s="44"/>
-      <c r="E103" s="44"/>
-      <c r="F103" s="44"/>
-      <c r="G103" s="44"/>
-      <c r="H103" s="44"/>
-      <c r="I103" s="44"/>
+      <c r="B103" s="41"/>
+      <c r="C103" s="41"/>
+      <c r="D103" s="41"/>
+      <c r="E103" s="41"/>
+      <c r="F103" s="41"/>
+      <c r="G103" s="41"/>
+      <c r="H103" s="41"/>
+      <c r="I103" s="41"/>
     </row>
     <row r="104" spans="1:9" s="31" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="35" t="s">
@@ -8207,17 +8207,17 @@
       </c>
     </row>
     <row r="107" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A107" s="43" t="s">
+      <c r="A107" s="40" t="s">
         <v>714</v>
       </c>
-      <c r="B107" s="44"/>
-      <c r="C107" s="44"/>
-      <c r="D107" s="44"/>
-      <c r="E107" s="44"/>
-      <c r="F107" s="44"/>
-      <c r="G107" s="44"/>
-      <c r="H107" s="44"/>
-      <c r="I107" s="44"/>
+      <c r="B107" s="41"/>
+      <c r="C107" s="41"/>
+      <c r="D107" s="41"/>
+      <c r="E107" s="41"/>
+      <c r="F107" s="41"/>
+      <c r="G107" s="41"/>
+      <c r="H107" s="41"/>
+      <c r="I107" s="41"/>
     </row>
     <row r="108" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="35" t="s">
@@ -8307,17 +8307,17 @@
       </c>
     </row>
     <row r="111" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A111" s="43" t="s">
+      <c r="A111" s="40" t="s">
         <v>735</v>
       </c>
-      <c r="B111" s="44"/>
-      <c r="C111" s="44"/>
-      <c r="D111" s="44"/>
-      <c r="E111" s="44"/>
-      <c r="F111" s="44"/>
-      <c r="G111" s="44"/>
-      <c r="H111" s="44"/>
-      <c r="I111" s="44"/>
+      <c r="B111" s="41"/>
+      <c r="C111" s="41"/>
+      <c r="D111" s="41"/>
+      <c r="E111" s="41"/>
+      <c r="F111" s="41"/>
+      <c r="G111" s="41"/>
+      <c r="H111" s="41"/>
+      <c r="I111" s="41"/>
     </row>
     <row r="112" spans="1:9" ht="100.8" x14ac:dyDescent="0.45">
       <c r="A112" s="35" t="s">
@@ -8465,17 +8465,17 @@
       </c>
     </row>
     <row r="117" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A117" s="43" t="s">
+      <c r="A117" s="40" t="s">
         <v>768</v>
       </c>
-      <c r="B117" s="44"/>
-      <c r="C117" s="44"/>
-      <c r="D117" s="44"/>
-      <c r="E117" s="44"/>
-      <c r="F117" s="44"/>
-      <c r="G117" s="44"/>
-      <c r="H117" s="44"/>
-      <c r="I117" s="44"/>
+      <c r="B117" s="41"/>
+      <c r="C117" s="41"/>
+      <c r="D117" s="41"/>
+      <c r="E117" s="41"/>
+      <c r="F117" s="41"/>
+      <c r="G117" s="41"/>
+      <c r="H117" s="41"/>
+      <c r="I117" s="41"/>
     </row>
     <row r="118" spans="1:9" ht="100.8" x14ac:dyDescent="0.45">
       <c r="A118" s="35" t="s">
@@ -8594,17 +8594,17 @@
       </c>
     </row>
     <row r="122" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A122" s="43" t="s">
+      <c r="A122" s="40" t="s">
         <v>795</v>
       </c>
-      <c r="B122" s="44"/>
-      <c r="C122" s="44"/>
-      <c r="D122" s="44"/>
-      <c r="E122" s="44"/>
-      <c r="F122" s="44"/>
-      <c r="G122" s="44"/>
-      <c r="H122" s="44"/>
-      <c r="I122" s="44"/>
+      <c r="B122" s="41"/>
+      <c r="C122" s="41"/>
+      <c r="D122" s="41"/>
+      <c r="E122" s="41"/>
+      <c r="F122" s="41"/>
+      <c r="G122" s="41"/>
+      <c r="H122" s="41"/>
+      <c r="I122" s="41"/>
     </row>
     <row r="123" spans="1:9" ht="100.8" x14ac:dyDescent="0.45">
       <c r="A123" s="35" t="s">
@@ -8694,17 +8694,17 @@
       </c>
     </row>
     <row r="126" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A126" s="43" t="s">
+      <c r="A126" s="40" t="s">
         <v>816</v>
       </c>
-      <c r="B126" s="44"/>
-      <c r="C126" s="44"/>
-      <c r="D126" s="44"/>
-      <c r="E126" s="44"/>
-      <c r="F126" s="44"/>
-      <c r="G126" s="44"/>
-      <c r="H126" s="44"/>
-      <c r="I126" s="44"/>
+      <c r="B126" s="41"/>
+      <c r="C126" s="41"/>
+      <c r="D126" s="41"/>
+      <c r="E126" s="41"/>
+      <c r="F126" s="41"/>
+      <c r="G126" s="41"/>
+      <c r="H126" s="41"/>
+      <c r="I126" s="41"/>
     </row>
     <row r="127" spans="1:9" ht="100.8" x14ac:dyDescent="0.45">
       <c r="A127" s="35" t="s">
@@ -8765,17 +8765,17 @@
       </c>
     </row>
     <row r="129" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A129" s="43" t="s">
+      <c r="A129" s="40" t="s">
         <v>831</v>
       </c>
-      <c r="B129" s="44"/>
-      <c r="C129" s="44"/>
-      <c r="D129" s="44"/>
-      <c r="E129" s="44"/>
-      <c r="F129" s="44"/>
-      <c r="G129" s="44"/>
-      <c r="H129" s="44"/>
-      <c r="I129" s="44"/>
+      <c r="B129" s="41"/>
+      <c r="C129" s="41"/>
+      <c r="D129" s="41"/>
+      <c r="E129" s="41"/>
+      <c r="F129" s="41"/>
+      <c r="G129" s="41"/>
+      <c r="H129" s="41"/>
+      <c r="I129" s="41"/>
     </row>
     <row r="130" spans="1:9" ht="115.2" x14ac:dyDescent="0.45">
       <c r="A130" s="35" t="s">
@@ -8865,30 +8865,30 @@
       </c>
     </row>
     <row r="133" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A133" s="45" t="s">
+      <c r="A133" s="42" t="s">
         <v>852</v>
       </c>
-      <c r="B133" s="46"/>
-      <c r="C133" s="46"/>
-      <c r="D133" s="46"/>
-      <c r="E133" s="46"/>
-      <c r="F133" s="46"/>
-      <c r="G133" s="46"/>
-      <c r="H133" s="46"/>
-      <c r="I133" s="46"/>
+      <c r="B133" s="43"/>
+      <c r="C133" s="43"/>
+      <c r="D133" s="43"/>
+      <c r="E133" s="43"/>
+      <c r="F133" s="43"/>
+      <c r="G133" s="43"/>
+      <c r="H133" s="43"/>
+      <c r="I133" s="43"/>
     </row>
     <row r="134" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A134" s="43" t="s">
+      <c r="A134" s="40" t="s">
         <v>853</v>
       </c>
-      <c r="B134" s="44"/>
-      <c r="C134" s="44"/>
-      <c r="D134" s="44"/>
-      <c r="E134" s="44"/>
-      <c r="F134" s="44"/>
-      <c r="G134" s="44"/>
-      <c r="H134" s="44"/>
-      <c r="I134" s="44"/>
+      <c r="B134" s="41"/>
+      <c r="C134" s="41"/>
+      <c r="D134" s="41"/>
+      <c r="E134" s="41"/>
+      <c r="F134" s="41"/>
+      <c r="G134" s="41"/>
+      <c r="H134" s="41"/>
+      <c r="I134" s="41"/>
     </row>
     <row r="135" spans="1:9" ht="86.4" x14ac:dyDescent="0.45">
       <c r="A135" s="35" t="s">
@@ -9007,17 +9007,17 @@
       </c>
     </row>
     <row r="139" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A139" s="43" t="s">
+      <c r="A139" s="40" t="s">
         <v>880</v>
       </c>
-      <c r="B139" s="44"/>
-      <c r="C139" s="44"/>
-      <c r="D139" s="44"/>
-      <c r="E139" s="44"/>
-      <c r="F139" s="44"/>
-      <c r="G139" s="44"/>
-      <c r="H139" s="44"/>
-      <c r="I139" s="44"/>
+      <c r="B139" s="41"/>
+      <c r="C139" s="41"/>
+      <c r="D139" s="41"/>
+      <c r="E139" s="41"/>
+      <c r="F139" s="41"/>
+      <c r="G139" s="41"/>
+      <c r="H139" s="41"/>
+      <c r="I139" s="41"/>
     </row>
     <row r="140" spans="1:9" ht="86.4" x14ac:dyDescent="0.45">
       <c r="A140" s="35" t="s">
@@ -9107,17 +9107,17 @@
       </c>
     </row>
     <row r="143" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A143" s="43" t="s">
+      <c r="A143" s="40" t="s">
         <v>901</v>
       </c>
-      <c r="B143" s="44"/>
-      <c r="C143" s="44"/>
-      <c r="D143" s="44"/>
-      <c r="E143" s="44"/>
-      <c r="F143" s="44"/>
-      <c r="G143" s="44"/>
-      <c r="H143" s="44"/>
-      <c r="I143" s="44"/>
+      <c r="B143" s="41"/>
+      <c r="C143" s="41"/>
+      <c r="D143" s="41"/>
+      <c r="E143" s="41"/>
+      <c r="F143" s="41"/>
+      <c r="G143" s="41"/>
+      <c r="H143" s="41"/>
+      <c r="I143" s="41"/>
     </row>
     <row r="144" spans="1:9" ht="86.4" x14ac:dyDescent="0.45">
       <c r="A144" s="35" t="s">
@@ -9207,17 +9207,17 @@
       </c>
     </row>
     <row r="147" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A147" s="43" t="s">
+      <c r="A147" s="40" t="s">
         <v>920</v>
       </c>
-      <c r="B147" s="44"/>
-      <c r="C147" s="44"/>
-      <c r="D147" s="44"/>
-      <c r="E147" s="44"/>
-      <c r="F147" s="44"/>
-      <c r="G147" s="44"/>
-      <c r="H147" s="44"/>
-      <c r="I147" s="44"/>
+      <c r="B147" s="41"/>
+      <c r="C147" s="41"/>
+      <c r="D147" s="41"/>
+      <c r="E147" s="41"/>
+      <c r="F147" s="41"/>
+      <c r="G147" s="41"/>
+      <c r="H147" s="41"/>
+      <c r="I147" s="41"/>
     </row>
     <row r="148" spans="1:9" ht="100.8" x14ac:dyDescent="0.45">
       <c r="A148" s="35" t="s">
@@ -9336,17 +9336,17 @@
       </c>
     </row>
     <row r="152" spans="1:9" ht="18.899999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A152" s="43" t="s">
+      <c r="A152" s="40" t="s">
         <v>947</v>
       </c>
-      <c r="B152" s="44"/>
-      <c r="C152" s="44"/>
-      <c r="D152" s="44"/>
-      <c r="E152" s="44"/>
-      <c r="F152" s="44"/>
-      <c r="G152" s="44"/>
-      <c r="H152" s="44"/>
-      <c r="I152" s="44"/>
+      <c r="B152" s="41"/>
+      <c r="C152" s="41"/>
+      <c r="D152" s="41"/>
+      <c r="E152" s="41"/>
+      <c r="F152" s="41"/>
+      <c r="G152" s="41"/>
+      <c r="H152" s="41"/>
+      <c r="I152" s="41"/>
     </row>
     <row r="153" spans="1:9" ht="86.4" x14ac:dyDescent="0.45">
       <c r="A153" s="35" t="s">
@@ -9495,26 +9495,18 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A79:I79"/>
-    <mergeCell ref="A87:I87"/>
-    <mergeCell ref="A126:I126"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="A147:I147"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A19:I19"/>
-    <mergeCell ref="A68:I68"/>
-    <mergeCell ref="A117:I117"/>
-    <mergeCell ref="A111:I111"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="A58:I58"/>
-    <mergeCell ref="A143:I143"/>
-    <mergeCell ref="A39:I39"/>
-    <mergeCell ref="A48:I48"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="A94:I94"/>
-    <mergeCell ref="A103:I103"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A129:I129"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A122:I122"/>
+    <mergeCell ref="A72:I72"/>
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A9:I9"/>
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A16:I16"/>
     <mergeCell ref="A152:I152"/>
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="A83:I83"/>
@@ -9531,20 +9523,28 @@
     <mergeCell ref="A33:I33"/>
     <mergeCell ref="A46:I46"/>
     <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A68:I68"/>
+    <mergeCell ref="A117:I117"/>
+    <mergeCell ref="A111:I111"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="A94:I94"/>
+    <mergeCell ref="A103:I103"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A79:I79"/>
+    <mergeCell ref="A87:I87"/>
+    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="A147:I147"/>
+    <mergeCell ref="A143:I143"/>
     <mergeCell ref="A139:I139"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A129:I129"/>
-    <mergeCell ref="A22:I22"/>
-    <mergeCell ref="A122:I122"/>
-    <mergeCell ref="A72:I72"/>
-    <mergeCell ref="A29:I29"/>
-    <mergeCell ref="A52:I52"/>
     <mergeCell ref="A134:I134"/>
-    <mergeCell ref="A6:I6"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -9552,27 +9552,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="76027dd9-77cd-484f-b6db-8bbe1351c2b5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="1046e879-d081-4053-adba-52e34fa7725d" xsi:nil="true"/>
-    <Comments xmlns="76027dd9-77cd-484f-b6db-8bbe1351c2b5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C634B67D360B774FBA94A353DF812505" ma:contentTypeVersion="22" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="36ad41d1389f7dc8fcbb5d4285216769">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="76027dd9-77cd-484f-b6db-8bbe1351c2b5" xmlns:ns3="1046e879-d081-4053-adba-52e34fa7725d" xmlns:ns4="13a0c8d5-cff5-4140-b58f-0947a5552a6a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f2fb244498141b944b4dbc5f58037586" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="76027dd9-77cd-484f-b6db-8bbe1351c2b5"/>
@@ -9846,33 +9825,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F00D1D03-D728-4FCC-8D12-B8950FAF17A2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="1046e879-d081-4053-adba-52e34fa7725d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="13a0c8d5-cff5-4140-b58f-0947a5552a6a"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="76027dd9-77cd-484f-b6db-8bbe1351c2b5"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A42F3CFC-C897-4556-A913-297D413ED195}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="76027dd9-77cd-484f-b6db-8bbe1351c2b5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="1046e879-d081-4053-adba-52e34fa7725d" xsi:nil="true"/>
+    <Comments xmlns="76027dd9-77cd-484f-b6db-8bbe1351c2b5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64E2D905-EE85-4A04-B03B-15478B0DFC7C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9890,4 +9864,30 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A42F3CFC-C897-4556-A913-297D413ED195}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F00D1D03-D728-4FCC-8D12-B8950FAF17A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="1046e879-d081-4053-adba-52e34fa7725d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="13a0c8d5-cff5-4140-b58f-0947a5552a6a"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="76027dd9-77cd-484f-b6db-8bbe1351c2b5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>